--- a/otera_data.xlsx
+++ b/otera_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSCode\AI寺院案内サイト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26DA0FC6-01CE-4BAE-A7B4-54962A725916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C904D56-1E0C-4DB1-8D26-BA91D2AD134B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{AE7F8EEF-1655-4A3C-90DE-128D966DC36B}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="84">
   <si>
     <t>name</t>
   </si>
@@ -31,12 +31,6 @@
     <t>address</t>
   </si>
   <si>
-    <t>access</t>
-  </si>
-  <si>
-    <t>detail</t>
-  </si>
-  <si>
     <t>caution</t>
   </si>
   <si>
@@ -49,9 +43,6 @@
     <t>山梨県富士吉田市下吉田３丁目２６−１８</t>
   </si>
   <si>
-    <t>富士急行線「月江寺駅」から徒歩5分</t>
-  </si>
-  <si>
     <t>地蔵寺</t>
   </si>
   <si>
@@ -76,27 +67,18 @@
     <t>山梨県南都留郡山中湖村平野１４７</t>
   </si>
   <si>
-    <t>富士急行バス「平野」バス停から徒歩圏内</t>
-  </si>
-  <si>
     <t>承天寺</t>
   </si>
   <si>
     <t>山梨県南都留郡忍野村内野１９２</t>
   </si>
   <si>
-    <t>富士急行バス「内野」バス停下車すぐ</t>
-  </si>
-  <si>
     <t>円通寺</t>
   </si>
   <si>
     <t>山梨県南都留郡富士河口湖町船津３９３２</t>
   </si>
   <si>
-    <t>河口湖周遊バス「猿まわし劇場木の花美術館」徒歩圏内</t>
-  </si>
-  <si>
     <t>一乗寺</t>
   </si>
   <si>
@@ -157,9 +139,6 @@
     <t>山梨県南都留郡富士河口湖町小立６９２</t>
   </si>
   <si>
-    <t>河口湖周遊バス「妙法寺入口」下車</t>
-  </si>
-  <si>
     <t>妙本寺</t>
   </si>
   <si>
@@ -175,9 +154,6 @@
     <t>山梨県南都留郡忍野村忍草３８</t>
   </si>
   <si>
-    <t>富士急行バス「忍野八海」バス停から徒歩5分</t>
-  </si>
-  <si>
     <t>聖德寺</t>
   </si>
   <si>
@@ -271,9 +247,6 @@
     <t>山梨県富士吉田市下吉田３丁目４１−１８</t>
   </si>
   <si>
-    <t>富士急行線「下吉田駅」から徒歩10分</t>
-  </si>
-  <si>
     <t>如来寺</t>
   </si>
   <si>
@@ -290,13 +263,22 @@
   </si>
   <si>
     <t>山梨県富士吉田市浅間１丁目５−３８</t>
+  </si>
+  <si>
+    <t>nokanshiyo</t>
+  </si>
+  <si>
+    <t>kakimono</t>
+  </si>
+  <si>
+    <t>flow</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -456,6 +438,13 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -638,7 +627,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -753,6 +742,226 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -882,8 +1091,62 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -931,7 +1194,223 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="良い" xfId="6" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thick">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -942,6 +1421,30 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E4A6BD6-F78D-40F3-BFF0-6CCA6B8E682F}" name="otera_data" displayName="otera_data" ref="A1:G42" totalsRowShown="0" headerRowDxfId="1" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+  <autoFilter ref="A1:G42" xr:uid="{2E4A6BD6-F78D-40F3-BFF0-6CCA6B8E682F}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{C9E74559-0C15-4B9B-8D5B-D7591F595809}" name="name" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{8BE6A29B-8C28-4265-BD48-F803B7CDD678}" name="sect" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{2FCD2332-E7AD-42C8-BC18-DD998381D8E6}" name="address" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{A06B0EFE-F96E-4B13-BED3-71F02832C8CD}" name="nokanshiyo" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{6CA6EE47-0C03-4FB0-B3CD-9AC8C543496A}" name="kakimono" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{4890FF0A-DEC9-49D4-BBAC-445F2711FEBF}" name="flow" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{F232B76E-9DF9-4B58-BFB4-1DC7DD75CF8A}" name="caution" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1241,437 +1744,626 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDFBFA24-2D04-4B2F-9707-E49620E914F0}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="11.375" customWidth="1"/>
+    <col min="2" max="2" width="11.125" customWidth="1"/>
+    <col min="3" max="3" width="42.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.75" customWidth="1"/>
+    <col min="5" max="5" width="28.125" customWidth="1"/>
+    <col min="6" max="6" width="22.375" customWidth="1"/>
+    <col min="7" max="7" width="28.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B2" s="8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="C2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="9"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="11"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="11"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="11"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" s="10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" s="10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D6" t="s">
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="11"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D8" t="s">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="11"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="11"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B14" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="14"/>
+    </row>
+    <row r="15" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="3"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B16" s="16" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
+      <c r="C16" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="17"/>
+    </row>
+    <row r="17" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="3"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="18"/>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="7" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
+      <c r="B18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="C18" s="8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="9"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="11"/>
+    </row>
+    <row r="20" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="12" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
+      <c r="B20" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="14"/>
+    </row>
+    <row r="21" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="3"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B22" s="8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
+      <c r="C22" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="9"/>
+    </row>
+    <row r="23" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D19" t="s">
+      <c r="B23" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="14"/>
+    </row>
+    <row r="24" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="3"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="18"/>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B25" s="8" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
+      <c r="C25" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="9"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C22" t="s">
+      <c r="B26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="11"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="10" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
+      <c r="B27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B23" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="11"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="10" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
+      <c r="B28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="11"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C25" t="s">
+      <c r="B29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="11"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="11"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="11"/>
+    </row>
+    <row r="32" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B32" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="13" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="14"/>
+    </row>
+    <row r="33" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="3"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="18"/>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B29" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B34" s="8" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
+      <c r="C34" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B30" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="9"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="10" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
+      <c r="B35" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B31" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="11"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="10" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
+      <c r="B36" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B32" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="11"/>
+    </row>
+    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="12" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
+      <c r="B37" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B34" t="s">
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="14"/>
+    </row>
+    <row r="38" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="3"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="18"/>
+    </row>
+    <row r="39" spans="1:7" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C34" t="s">
+      <c r="B39" s="8" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
+      <c r="C39" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B35" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="9"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="10" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
+      <c r="B40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="11"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
+      <c r="B41" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="11"/>
+    </row>
+    <row r="42" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="12" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A39" t="s">
+      <c r="B42" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B39" t="s">
-        <v>81</v>
-      </c>
-      <c r="C39" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A40" t="s">
-        <v>84</v>
-      </c>
-      <c r="B40" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
-        <v>86</v>
-      </c>
-      <c r="B41" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A42" t="s">
-        <v>88</v>
-      </c>
-      <c r="B42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C42" t="s">
-        <v>89</v>
-      </c>
-    </row>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="14"/>
+    </row>
+    <row r="43" spans="1:7" ht="19.5" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>